--- a/unidades.xlsx
+++ b/unidades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://expresodiemar-my.sharepoint.com/personal/nicolascolonna_expresodiemar_onmicrosoft_com/Documents/COMBUSTIBLE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="11_229D4A3F10749CAE6C5274D65D5DCE3A47C94ABF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E4BA23C-9CEB-7E45-AA46-E03939FBE742}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="11_229D4A3F10749CAE6C5274D65D5DCE3A47C94ABF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{207CC569-A33C-AB4E-86E8-15FDA8E62CD6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>Tiempo funcionamiento motor (h:m)</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>DOMINIO</t>
+  </si>
+  <si>
+    <t>q</t>
   </si>
 </sst>
 </file>
@@ -891,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E1048573"/>
+  <dimension ref="A1:P1048573"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="6" bestFit="1" customWidth="1"/>
@@ -1173,7 +1176,7 @@
         <v>514.79999999999995</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="23">
         <v>46053</v>
       </c>
@@ -1190,7 +1193,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" s="23">
         <v>46053</v>
       </c>
@@ -1204,8 +1207,11 @@
       <c r="E18" s="8">
         <v>14508.414076000001</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="P18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" s="23">
         <v>46053</v>
       </c>
@@ -1220,7 +1226,7 @@
         <v>12467.140531999999</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20" s="23">
         <v>46053</v>
       </c>
@@ -1235,7 +1241,7 @@
         <v>11604.694287</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D21" s="21"/>
     </row>
     <row r="1048573" spans="1:5" x14ac:dyDescent="0.2">
